--- a/data/tenipuriwaza.xlsx
+++ b/data/tenipuriwaza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C623544B-A756-4537-BB3D-7090972E04C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{C623544B-A756-4537-BB3D-7090972E04C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C3F483-0BF6-42CD-A835-EFAAE1BED41E}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1740" windowWidth="15330" windowHeight="11880" xr2:uid="{CCE97F10-6A64-4B3A-A256-1E7085600B75}"/>
+    <workbookView xWindow="3690" yWindow="5295" windowWidth="14805" windowHeight="9930" xr2:uid="{CCE97F10-6A64-4B3A-A256-1E7085600B75}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17590" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17689" uniqueCount="874">
   <si>
     <t>誰が</t>
     <rPh sb="0" eb="1">
@@ -6970,6 +6970,412 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>セップク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新198</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>真田・幸村</t>
+    <rPh sb="0" eb="2">
+      <t>サナダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ユキムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鉄壁の守備（アイアンウォール）</t>
+    <rPh sb="0" eb="2">
+      <t>テッペキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界大会Bブロック2回戦D1</t>
+    <rPh sb="0" eb="4">
+      <t>セカイタイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新199</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>真田弦一郎</t>
+    <rPh sb="0" eb="5">
+      <t>サナダゲンイチロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャン・フィッツジェラルド＆
+クリス・ホップマン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒龍二重の斬</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フタエ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポイント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャン・フィッツジェラルド</t>
+  </si>
+  <si>
+    <t>黒龍一重の斬</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒトエ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新200</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返球</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新201</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徐かなること林の如し</t>
+    <rPh sb="0" eb="1">
+      <t>ジョ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハヤシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミルキー・ミルマン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不二周助</t>
+    <rPh sb="0" eb="4">
+      <t>フジシュウスケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新203</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tachyon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界大会Bブロック2回戦D2</t>
+    <rPh sb="0" eb="4">
+      <t>セカイタイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>跡部景吾</t>
+    <rPh sb="0" eb="4">
+      <t>アトベケイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新205</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羆落とし</t>
+    <rPh sb="0" eb="1">
+      <t>ヒグマ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Neutrino</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新206</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破滅への輪舞曲</t>
+    <rPh sb="0" eb="2">
+      <t>ハメツ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リンブキョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27-27</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>光風</t>
+    <rPh sb="0" eb="2">
+      <t>ヒカリカゼ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風の攻撃技（クリティカルウインド）
+147-146</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新207</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷の皇帝（エンペラー）</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>148－146</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠山金太郎</t>
+    <rPh sb="0" eb="2">
+      <t>トオヤマ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キンタロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J・J・ドルギアス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新209</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全国大会決勝D2</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンコクタイカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天衣無縫の極み</t>
+    <rPh sb="0" eb="4">
+      <t>テンイムホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界大会Bブロック2回戦S3</t>
+    <rPh sb="0" eb="4">
+      <t>セカイタイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超メガトンワンダーデラックス山噴火サーブ</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ヤマフンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新216</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界大会Bブロック3回戦D1</t>
+    <rPh sb="0" eb="4">
+      <t>セカイタイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>裏三十六式波動球</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="1" eb="5">
+      <t>サンジュウロクシキ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ハドウキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石田銀</t>
+    <rPh sb="0" eb="2">
+      <t>イシダ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ギン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルバート・フェデラー＆
+ランディ・プグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界大会Bブロック3回戦S3</t>
+    <rPh sb="0" eb="4">
+      <t>セカイタイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亜久津仁</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -64657,7 +65063,7 @@
         <v>438</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>439</v>
+        <v>861</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>321</v>
@@ -64681,7 +65087,7 @@
         <v>442</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>439</v>
+        <v>861</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>321</v>
@@ -64705,7 +65111,7 @@
         <v>381</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>439</v>
+        <v>861</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>321</v>
@@ -64720,7 +65126,7 @@
         <v>446</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>360</v>
+        <v>132</v>
       </c>
       <c r="C334" s="2">
         <v>356</v>
@@ -64729,7 +65135,7 @@
         <v>447</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>439</v>
+        <v>861</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>321</v>
@@ -64753,7 +65159,7 @@
         <v>448</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>439</v>
+        <v>861</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>321</v>
@@ -64777,7 +65183,7 @@
         <v>381</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>439</v>
+        <v>861</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>321</v>
@@ -68976,152 +69382,350 @@
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A511" s="2"/>
-      <c r="B511" s="2"/>
-      <c r="C511" s="2"/>
-      <c r="D511" s="2"/>
-      <c r="E511" s="2"/>
+    <row r="511" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A511" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C511" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E511" s="2" t="s">
+        <v>844</v>
+      </c>
       <c r="F511" s="2"/>
       <c r="G511" s="2"/>
       <c r="H511" s="2"/>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A512" s="2"/>
-      <c r="B512" s="2"/>
-      <c r="C512" s="2"/>
-      <c r="D512" s="2"/>
-      <c r="E512" s="2"/>
-      <c r="F512" s="2"/>
-      <c r="G512" s="2"/>
+    <row r="512" spans="1:8" ht="33" x14ac:dyDescent="0.4">
+      <c r="A512" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B512" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="D512" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="E512" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F512" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G512" s="2" t="s">
+        <v>833</v>
+      </c>
       <c r="H512" s="2"/>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A513" s="2"/>
-      <c r="B513" s="2"/>
-      <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
-      <c r="E513" s="2"/>
-      <c r="F513" s="2"/>
-      <c r="G513" s="2"/>
+      <c r="A513" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C513" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="D513" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E513" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F513" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G513" s="2" t="s">
+        <v>837</v>
+      </c>
       <c r="H513" s="2"/>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A514" s="2"/>
-      <c r="B514" s="2"/>
-      <c r="C514" s="2"/>
-      <c r="D514" s="2"/>
-      <c r="E514" s="2"/>
-      <c r="F514" s="2"/>
-      <c r="G514" s="2"/>
+    <row r="514" spans="1:8" ht="33" x14ac:dyDescent="0.4">
+      <c r="A514" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B514" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="C514" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="D514" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="E514" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F514" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G514" s="2" t="s">
+        <v>837</v>
+      </c>
       <c r="H514" s="2"/>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A515" s="2"/>
-      <c r="B515" s="2"/>
-      <c r="C515" s="2"/>
-      <c r="D515" s="2"/>
-      <c r="E515" s="2"/>
-      <c r="F515" s="2"/>
-      <c r="G515" s="2"/>
+      <c r="A515" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="E515" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F515" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G515" s="2" t="s">
+        <v>845</v>
+      </c>
       <c r="H515" s="2"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A516" s="2"/>
-      <c r="B516" s="2"/>
-      <c r="C516" s="2"/>
-      <c r="D516" s="2"/>
-      <c r="E516" s="2"/>
-      <c r="F516" s="2"/>
-      <c r="G516" s="2"/>
+      <c r="A516" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F516" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G516" s="2" t="s">
+        <v>837</v>
+      </c>
       <c r="H516" s="2"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A517" s="2"/>
-      <c r="B517" s="2"/>
-      <c r="C517" s="2"/>
-      <c r="D517" s="2"/>
-      <c r="E517" s="2"/>
-      <c r="F517" s="2"/>
-      <c r="G517" s="2"/>
+      <c r="A517" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F517" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G517" s="2" t="s">
+        <v>833</v>
+      </c>
       <c r="H517" s="2"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A518" s="2"/>
-      <c r="B518" s="2"/>
-      <c r="C518" s="2"/>
-      <c r="D518" s="2"/>
-      <c r="E518" s="2"/>
-      <c r="F518" s="2"/>
-      <c r="G518" s="2"/>
+      <c r="A518" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F518" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G518" s="2" t="s">
+        <v>837</v>
+      </c>
       <c r="H518" s="2"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A519" s="2"/>
-      <c r="B519" s="2"/>
-      <c r="C519" s="2"/>
-      <c r="D519" s="2"/>
-      <c r="E519" s="2"/>
-      <c r="F519" s="2"/>
-      <c r="G519" s="2"/>
-      <c r="H519" s="2"/>
+      <c r="A519" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="H519" s="2" t="s">
+        <v>852</v>
+      </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A520" s="2"/>
-      <c r="B520" s="2"/>
-      <c r="C520" s="2"/>
-      <c r="D520" s="2"/>
-      <c r="E520" s="2"/>
-      <c r="F520" s="2"/>
-      <c r="G520" s="2"/>
-      <c r="H520" s="2"/>
+    <row r="520" spans="1:8" ht="33" x14ac:dyDescent="0.4">
+      <c r="A520" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B520" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="C520" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="H520" s="13" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A521" s="2"/>
-      <c r="B521" s="2"/>
-      <c r="C521" s="2"/>
-      <c r="D521" s="2"/>
-      <c r="E521" s="2"/>
-      <c r="F521" s="2"/>
-      <c r="G521" s="2"/>
-      <c r="H521" s="2"/>
+      <c r="A521" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C521" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="H521" s="2" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A522" s="2"/>
-      <c r="B522" s="2"/>
-      <c r="C522" s="2"/>
-      <c r="D522" s="2"/>
-      <c r="E522" s="2"/>
-      <c r="F522" s="2"/>
+      <c r="A522" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>864</v>
+      </c>
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A523" s="2"/>
-      <c r="B523" s="2"/>
-      <c r="C523" s="2"/>
-      <c r="D523" s="2"/>
-      <c r="E523" s="2"/>
-      <c r="F523" s="2"/>
-      <c r="G523" s="2"/>
+      <c r="A523" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C523" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="D523" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H523" s="2"/>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A524" s="2"/>
-      <c r="B524" s="2"/>
-      <c r="C524" s="2"/>
-      <c r="D524" s="2"/>
-      <c r="E524" s="2"/>
-      <c r="F524" s="2"/>
+    <row r="524" spans="1:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A524" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B524" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>872</v>
+      </c>
       <c r="G524" s="2"/>
       <c r="H524" s="2"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A525" s="2"/>
+      <c r="A525" s="2" t="s">
+        <v>873</v>
+      </c>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
       <c r="D525" s="2"/>
-      <c r="E525" s="2"/>
+      <c r="E525" s="2" t="s">
+        <v>871</v>
+      </c>
       <c r="F525" s="2"/>
       <c r="G525" s="2"/>
       <c r="H525" s="2"/>
